--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,227 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118847687</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 27727, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579405</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398324</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118847592</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94620</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 27727, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579531</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118608477</v>
+        <v>118609828</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579312</v>
+        <v>579427</v>
       </c>
       <c r="R2" t="n">
-        <v>6398154</v>
+        <v>6398257</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118609828</v>
+        <v>118610366</v>
       </c>
       <c r="B3" t="n">
         <v>57306</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579427</v>
+        <v>579484</v>
       </c>
       <c r="R3" t="n">
-        <v>6398257</v>
+        <v>6398383</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118610366</v>
+        <v>118608477</v>
       </c>
       <c r="B4" t="n">
         <v>57306</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579484</v>
+        <v>579312</v>
       </c>
       <c r="R4" t="n">
-        <v>6398383</v>
+        <v>6398154</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847687</v>
+        <v>118847592</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,39 +1155,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579405</v>
+        <v>579531</v>
       </c>
       <c r="R6" t="n">
-        <v>6398324</v>
+        <v>6398442</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847592</v>
+        <v>118847687</v>
       </c>
       <c r="B7" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,31 +1262,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579531</v>
+        <v>579405</v>
       </c>
       <c r="R7" t="n">
-        <v>6398442</v>
+        <v>6398324</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118610366</v>
+        <v>118610712</v>
       </c>
       <c r="B3" t="n">
         <v>57306</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579484</v>
+        <v>579433</v>
       </c>
       <c r="R3" t="n">
-        <v>6398383</v>
+        <v>6398430</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118610712</v>
+        <v>118610366</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579433</v>
+        <v>579484</v>
       </c>
       <c r="R5" t="n">
-        <v>6398430</v>
+        <v>6398383</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847592</v>
+        <v>118847687</v>
       </c>
       <c r="B6" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,31 +1155,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579531</v>
+        <v>579405</v>
       </c>
       <c r="R6" t="n">
-        <v>6398442</v>
+        <v>6398324</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1239,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847687</v>
+        <v>118847592</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>94620</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1269,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579405</v>
+        <v>579531</v>
       </c>
       <c r="R7" t="n">
-        <v>6398324</v>
+        <v>6398442</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118609828</v>
+        <v>118608477</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579427</v>
+        <v>579312</v>
       </c>
       <c r="R2" t="n">
-        <v>6398257</v>
+        <v>6398154</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118610712</v>
+        <v>118610366</v>
       </c>
       <c r="B3" t="n">
         <v>57306</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579433</v>
+        <v>579484</v>
       </c>
       <c r="R3" t="n">
-        <v>6398430</v>
+        <v>6398383</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118608477</v>
+        <v>118609828</v>
       </c>
       <c r="B4" t="n">
         <v>57306</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579312</v>
+        <v>579427</v>
       </c>
       <c r="R4" t="n">
-        <v>6398154</v>
+        <v>6398257</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118610366</v>
+        <v>118610712</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579484</v>
+        <v>579433</v>
       </c>
       <c r="R5" t="n">
-        <v>6398383</v>
+        <v>6398430</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847687</v>
+        <v>118847592</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,39 +1155,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579405</v>
+        <v>579531</v>
       </c>
       <c r="R6" t="n">
-        <v>6398324</v>
+        <v>6398442</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847592</v>
+        <v>118847687</v>
       </c>
       <c r="B7" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,31 +1262,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579531</v>
+        <v>579405</v>
       </c>
       <c r="R7" t="n">
-        <v>6398442</v>
+        <v>6398324</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118608477</v>
+        <v>118610712</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579312</v>
+        <v>579433</v>
       </c>
       <c r="R2" t="n">
-        <v>6398154</v>
+        <v>6398430</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118610712</v>
+        <v>118608477</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579433</v>
+        <v>579312</v>
       </c>
       <c r="R5" t="n">
-        <v>6398430</v>
+        <v>6398154</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847592</v>
+        <v>118847687</v>
       </c>
       <c r="B6" t="n">
-        <v>94627</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,31 +1155,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579531</v>
+        <v>579405</v>
       </c>
       <c r="R6" t="n">
-        <v>6398442</v>
+        <v>6398324</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1239,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847687</v>
+        <v>118847592</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1269,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579405</v>
+        <v>579531</v>
       </c>
       <c r="R7" t="n">
-        <v>6398324</v>
+        <v>6398442</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119624174</v>
+        <v>119608145</v>
       </c>
       <c r="B9" t="n">
-        <v>57316</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579371</v>
+        <v>579299</v>
       </c>
       <c r="R9" t="n">
-        <v>6398423</v>
+        <v>6398361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,17 +1563,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119608145</v>
+        <v>119608229</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>90582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,35 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1652,13 +1646,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579299</v>
+        <v>579346</v>
       </c>
       <c r="R10" t="n">
-        <v>6398361</v>
+        <v>6398406</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,6 +1690,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1714,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119608229</v>
+        <v>119624139</v>
       </c>
       <c r="B11" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,34 +1725,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1765,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579346</v>
+        <v>579421</v>
       </c>
       <c r="R11" t="n">
-        <v>6398406</v>
+        <v>6398260</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,12 +1787,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1806,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1828,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624139</v>
+        <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>57316</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,16 +1840,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1861,12 +1857,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1876,13 +1876,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579421</v>
+        <v>579371</v>
       </c>
       <c r="R12" t="n">
-        <v>6398260</v>
+        <v>6398423</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119608145</v>
+        <v>119624174</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>57316</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579299</v>
+        <v>579371</v>
       </c>
       <c r="R9" t="n">
-        <v>6398361</v>
+        <v>6398423</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,12 +1563,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119608229</v>
+        <v>119624139</v>
       </c>
       <c r="B10" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,34 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1646,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579346</v>
+        <v>579421</v>
       </c>
       <c r="R10" t="n">
-        <v>6398406</v>
+        <v>6398260</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,12 +1678,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1697,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624139</v>
+        <v>119608145</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,29 +1731,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1757,13 +1767,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579421</v>
+        <v>579299</v>
       </c>
       <c r="R11" t="n">
-        <v>6398260</v>
+        <v>6398361</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,17 +1797,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624174</v>
+        <v>119608229</v>
       </c>
       <c r="B12" t="n">
-        <v>57316</v>
+        <v>90582</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,21 +1845,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1862,13 +1867,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1876,13 +1880,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579371</v>
+        <v>579346</v>
       </c>
       <c r="R12" t="n">
-        <v>6398423</v>
+        <v>6398406</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,17 +1910,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,6 +1924,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119624174</v>
+        <v>119624139</v>
       </c>
       <c r="B9" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,16 +1514,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1533,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579371</v>
+        <v>579421</v>
       </c>
       <c r="R9" t="n">
-        <v>6398423</v>
+        <v>6398260</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1569,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>Bearbetat låga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119624139</v>
+        <v>119608229</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>90582</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,31 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579421</v>
+        <v>579346</v>
       </c>
       <c r="R10" t="n">
-        <v>6398260</v>
+        <v>6398406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,17 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,6 +1691,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1829,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119608229</v>
+        <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>90582</v>
+        <v>57316</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,21 +1840,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1867,12 +1862,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1880,13 +1876,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579346</v>
+        <v>579371</v>
       </c>
       <c r="R12" t="n">
-        <v>6398406</v>
+        <v>6398423</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,12 +1906,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,7 +1925,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57316</v>
+        <v>57484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>119624174</v>
       </c>
       <c r="B12" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27727-2024 artfynd.xlsx
+++ b/artfynd/A 27727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118610712</v>
+        <v>119624335</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kammarbogöl (Kammarbogöl), Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579433</v>
+        <v>579317</v>
       </c>
       <c r="R2" t="n">
-        <v>6398430</v>
+        <v>6398111</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +765,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118610366</v>
+        <v>119266053</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,42 +795,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kammarbogöl (Kammarbogöl), Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579484</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6398383</v>
+        <v>6398252</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,76 +884,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118608477</v>
+        <v>118847592</v>
       </c>
       <c r="B4" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kammarbogöl (Kammarbogöl), Sm</t>
+          <t>A 27727, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579312</v>
+        <v>579531</v>
       </c>
       <c r="R4" t="n">
-        <v>6398154</v>
+        <v>6398442</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,76 +986,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118609828</v>
+        <v>119266069</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kammarbogöl (Kammarbogöl), Sm</t>
+          <t>A 27727, ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579427</v>
+        <v>579282</v>
       </c>
       <c r="R5" t="n">
-        <v>6398257</v>
+        <v>6398340</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1074,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,33 +1098,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118847687</v>
+        <v>119608229</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1181,27 +1150,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579405</v>
+        <v>579346</v>
       </c>
       <c r="R6" t="n">
-        <v>6398324</v>
+        <v>6398406</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1207,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1257,54 +1226,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118847592</v>
+        <v>105920013</v>
       </c>
       <c r="B7" t="n">
-        <v>94632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27727, Stormbo, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579531</v>
+        <v>579189</v>
       </c>
       <c r="R7" t="n">
-        <v>6398442</v>
+        <v>6398315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,12 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,54 +1335,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119266069</v>
+        <v>131732492</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 27727, ankarsrum, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579282</v>
+        <v>579297</v>
       </c>
       <c r="R8" t="n">
-        <v>6398340</v>
+        <v>6398143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,22 +1400,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,77 +1414,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119624139</v>
+        <v>131737000</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579421</v>
+        <v>579356</v>
       </c>
       <c r="R9" t="n">
-        <v>6398260</v>
+        <v>6398090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,17 +1501,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bearbetat låga</t>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,27 +1526,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119608229</v>
+        <v>119624174</v>
       </c>
       <c r="B10" t="n">
-        <v>90582</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1634,12 +1575,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,13 +1589,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579346</v>
+        <v>579371</v>
       </c>
       <c r="R10" t="n">
-        <v>6398406</v>
+        <v>6398423</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1619,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I ansl mindre blötmark.utning till</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,7 +1638,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1710,65 +1656,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119608145</v>
+        <v>118608477</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579299</v>
+        <v>579312</v>
       </c>
       <c r="R11" t="n">
-        <v>6398361</v>
+        <v>6398154</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,12 +1726,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,44 +1756,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624174</v>
+        <v>118609828</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1857,32 +1796,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579371</v>
+        <v>579427</v>
       </c>
       <c r="R12" t="n">
-        <v>6398423</v>
+        <v>6398257</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,17 +1838,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I ansl mindre blötmark.utning till</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,15 +1868,1092 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118610366</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579484</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398383</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118610712</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398430</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118611275</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kammartorp, Kammartorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579275</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398015</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118847687</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 27727, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579405</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398324</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119624115</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 27727, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579298</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398158</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119624139</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 27727, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579421</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398260</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119608145</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 27727, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579299</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6398361</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131740066</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kammarbogöl Nord, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579528</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6398236</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118564572</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579210</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6398292</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
